--- a/assessment_forms/021_internet_listening_assessment--assessment_forms.xlsx
+++ b/assessment_forms/021_internet_listening_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,8 +773,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -802,12 +802,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_5_hours_a_day'}</t>
+          <t>less_than_5_hours_a_day</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 5 hours a day'}</t>
+          <t>Less than 5 hours a day</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'5-10_hours_a_day'}</t>
+          <t>5-10_hours_a_day</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '5-10 hours a day'}</t>
+          <t>5-10 hours a day</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_10_hours_a_day'}</t>
+          <t>more_than_10_hours_a_day</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'More than 10 hours a day'}</t>
+          <t>More than 10 hours a day</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'browsing_and_navigating'}</t>
+          <t>browsing_and_navigating</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Browsing and navigating'}</t>
+          <t>Browsing and navigating</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'online_searching_and_research'}</t>
+          <t>online_searching_and_research</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Online searching and research'}</t>
+          <t>Online searching and research</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'online_communication_and_interaction'}</t>
+          <t>online_communication_and_interaction</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Online communication and interaction'}</t>
+          <t>Online communication and interaction</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'online_learning_and_education'}</t>
+          <t>online_learning_and_education</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Online learning and education'}</t>
+          <t>Online learning and education</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'limited_internet_access'}</t>
+          <t>limited_internet_access</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Limited internet access'}</t>
+          <t>Limited internet access</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'slow_internet_speed'}</t>
+          <t>slow_internet_speed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Slow internet speed'}</t>
+          <t>Slow internet speed</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'difficulty_understanding_online_content'}</t>
+          <t>difficulty_understanding_online_content</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Difficulty understanding online content'}</t>
+          <t>Difficulty understanding online content</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
